--- a/exports/trend_1d/SHRIRAMFIN_full_report.xlsx
+++ b/exports/trend_1d/SHRIRAMFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>218.25</v>
+        <v>213.4</v>
       </c>
       <c r="I2" t="n">
         <v>216.3002475090435</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>0.83</v>
+        <v>-1.41</v>
       </c>
       <c r="L2" t="n">
         <v>4.78</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.92</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42174</v>
+        <v>42177</v>
       </c>
       <c r="H3" t="n">
-        <v>172.5</v>
+        <v>173.7</v>
       </c>
       <c r="I3" t="n">
         <v>172.8529146857254</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K3" t="n">
-        <v>19.17</v>
+        <v>18.6</v>
       </c>
       <c r="L3" t="n">
         <v>10.22</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.37</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H4" t="n">
-        <v>166.8</v>
+        <v>160.75</v>
       </c>
       <c r="I4" t="n">
         <v>163.7679199683703</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.97</v>
+        <v>-7.46</v>
       </c>
       <c r="L4" t="n">
-        <v>5.76</v>
+        <v>8.09</v>
       </c>
       <c r="M4" t="n">
         <v>2.73</v>
       </c>
       <c r="N4" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="O4" t="n">
         <v>0.7</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>13.13</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42263</v>
+        <v>42265</v>
       </c>
       <c r="H5" t="n">
-        <v>170.2</v>
+        <v>177.05</v>
       </c>
       <c r="I5" t="n">
         <v>176.9271120091395</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.88</v>
+        <v>-10.14</v>
       </c>
       <c r="L5" t="n">
-        <v>9.050000000000001</v>
+        <v>10.67</v>
       </c>
       <c r="M5" t="n">
         <v>2.91</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.52</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H6" t="n">
-        <v>181.65</v>
+        <v>173.4</v>
       </c>
       <c r="I6" t="n">
         <v>173.6597830313275</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>-2.06</v>
       </c>
       <c r="L6" t="n">
         <v>4.8</v>
@@ -783,7 +854,7 @@
         <v>1.19</v>
       </c>
       <c r="N6" t="n">
-        <v>4.45</v>
+        <v>4.54</v>
       </c>
       <c r="O6" t="n">
         <v>4.02</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.38</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42369</v>
+        <v>42370</v>
       </c>
       <c r="H7" t="n">
-        <v>167.35</v>
+        <v>168.7</v>
       </c>
       <c r="I7" t="n">
         <v>168.6066255172582</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>3.49</v>
+        <v>2.71</v>
       </c>
       <c r="L7" t="n">
         <v>3.95</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>7.41</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42382</v>
+        <v>42383</v>
       </c>
       <c r="H8" t="n">
-        <v>157.2</v>
+        <v>155.85</v>
       </c>
       <c r="I8" t="n">
         <v>156.8540360145232</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.82</v>
+        <v>-7.62</v>
       </c>
       <c r="L8" t="n">
-        <v>9.16</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
         <v>5.85</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H9" t="n">
-        <v>146.3</v>
+        <v>164.5</v>
       </c>
       <c r="I9" t="n">
         <v>161.0419661565215</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>6.13</v>
+        <v>-5.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.83</v>
+        <v>7.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.35</v>
       </c>
       <c r="N9" t="n">
-        <v>1.56</v>
+        <v>12.44</v>
       </c>
       <c r="O9" t="n">
         <v>-0.86</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>17.08</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42571</v>
+        <v>42572</v>
       </c>
       <c r="H10" t="n">
-        <v>232.4</v>
+        <v>227.35</v>
       </c>
       <c r="I10" t="n">
         <v>231.0947987875623</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K10" t="n">
-        <v>41.28</v>
+        <v>38.21</v>
       </c>
       <c r="L10" t="n">
         <v>11.4</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.19</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="H11" t="n">
-        <v>249.45</v>
+        <v>253.05</v>
       </c>
       <c r="I11" t="n">
         <v>251.6922319569067</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.720000000000001</v>
+        <v>-11.3</v>
       </c>
       <c r="L11" t="n">
-        <v>13.31</v>
+        <v>13.53</v>
       </c>
       <c r="M11" t="n">
         <v>0.59</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.67</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42625</v>
+        <v>42627</v>
       </c>
       <c r="H12" t="n">
-        <v>229</v>
+        <v>225.2</v>
       </c>
       <c r="I12" t="n">
         <v>228.5982601474102</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.5</v>
+        <v>-11.01</v>
       </c>
       <c r="L12" t="n">
-        <v>9.9</v>
+        <v>12.59</v>
       </c>
       <c r="M12" t="n">
         <v>0.9399999999999999</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.35</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H13" t="n">
-        <v>166.3</v>
+        <v>172.35</v>
       </c>
       <c r="I13" t="n">
         <v>171.9423722494329</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K13" t="n">
-        <v>26.15</v>
+        <v>23.47</v>
       </c>
       <c r="L13" t="n">
         <v>8.59</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.64</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42859</v>
+        <v>42860</v>
       </c>
       <c r="H14" t="n">
-        <v>198.7</v>
+        <v>195.05</v>
       </c>
       <c r="I14" t="n">
         <v>195.8938303925697</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K14" t="n">
-        <v>15.29</v>
+        <v>13.17</v>
       </c>
       <c r="L14" t="n">
         <v>3.34</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.69</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42916</v>
+        <v>42919</v>
       </c>
       <c r="H15" t="n">
-        <v>194.85</v>
+        <v>200.5</v>
       </c>
       <c r="I15" t="n">
         <v>200.4088178713105</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1</v>
+        <v>-2.79</v>
       </c>
       <c r="L15" t="n">
         <v>4.1</v>
@@ -1296,7 +1475,7 @@
         <v>2.91</v>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>-1.84</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42926</v>
+        <v>42927</v>
       </c>
       <c r="H16" t="n">
-        <v>205.7</v>
+        <v>197.6</v>
       </c>
       <c r="I16" t="n">
         <v>198.9991243597063</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>2.59</v>
+        <v>-1.45</v>
       </c>
       <c r="L16" t="n">
         <v>3.34</v>
@@ -1353,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="O16" t="n">
         <v>2.9</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>17</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42979</v>
+        <v>42982</v>
       </c>
       <c r="H17" t="n">
-        <v>198.7</v>
+        <v>208.65</v>
       </c>
       <c r="I17" t="n">
         <v>202.7939773403704</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-5.59</v>
       </c>
       <c r="L17" t="n">
-        <v>4.83</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
         <v>1.33</v>
       </c>
       <c r="N17" t="n">
-        <v>4.84</v>
+        <v>5.01</v>
       </c>
       <c r="O17" t="n">
         <v>-3.94</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>11.97</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H18" t="n">
-        <v>207.7</v>
+        <v>195.1</v>
       </c>
       <c r="I18" t="n">
         <v>195.4106004301222</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.46</v>
+        <v>-6.49</v>
       </c>
       <c r="L18" t="n">
-        <v>6.57</v>
+        <v>7.79</v>
       </c>
       <c r="M18" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>6.07</v>
       </c>
       <c r="O18" t="n">
         <v>5.01</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>13.03</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43018</v>
+        <v>43019</v>
       </c>
       <c r="H19" t="n">
-        <v>210.7</v>
+        <v>214.3</v>
       </c>
       <c r="I19" t="n">
         <v>213.5111138020171</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>-8</v>
+        <v>-9.84</v>
       </c>
       <c r="L19" t="n">
-        <v>9.07</v>
+        <v>12.28</v>
       </c>
       <c r="M19" t="n">
         <v>3.31</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H20" t="n">
-        <v>278.95</v>
+        <v>267.9</v>
       </c>
       <c r="I20" t="n">
         <v>277.800047458607</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K20" t="n">
-        <v>30.17</v>
+        <v>25.01</v>
       </c>
       <c r="L20" t="n">
         <v>4.46</v>
@@ -1581,7 +1820,7 @@
         <v>1.83</v>
       </c>
       <c r="N20" t="n">
-        <v>3.24</v>
+        <v>3.96</v>
       </c>
       <c r="O20" t="n">
         <v>1.71</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>13</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="H21" t="n">
-        <v>268.15</v>
+        <v>284.65</v>
       </c>
       <c r="I21" t="n">
         <v>280.9534371863259</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.09</v>
+        <v>-6.25</v>
       </c>
       <c r="L21" t="n">
-        <v>4.67</v>
+        <v>6.74</v>
       </c>
       <c r="M21" t="n">
         <v>1.43</v>
       </c>
       <c r="N21" t="n">
-        <v>2.91</v>
+        <v>6.15</v>
       </c>
       <c r="O21" t="n">
         <v>-3.96</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.65</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43230</v>
+        <v>43231</v>
       </c>
       <c r="H22" t="n">
-        <v>292.25</v>
+        <v>289.85</v>
       </c>
       <c r="I22" t="n">
         <v>291.6747931762615</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K22" t="n">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="L22" t="n">
         <v>6.9</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.09</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H23" t="n">
-        <v>250.15</v>
+        <v>274.95</v>
       </c>
       <c r="I23" t="n">
         <v>257.4270392293372</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K23" t="n">
-        <v>13.7</v>
+        <v>5.14</v>
       </c>
       <c r="L23" t="n">
         <v>4.54</v>
@@ -1752,7 +2027,7 @@
         <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>5.71</v>
+        <v>9.91</v>
       </c>
       <c r="O23" t="n">
         <v>-0.82</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>18.23</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H24" t="n">
-        <v>252.8</v>
+        <v>245.5</v>
       </c>
       <c r="I24" t="n">
         <v>247.6859434164221</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.06</v>
+        <v>-10.71</v>
       </c>
       <c r="L24" t="n">
-        <v>9.42</v>
+        <v>10.91</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.98</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H25" t="n">
-        <v>227</v>
+        <v>236.45</v>
       </c>
       <c r="I25" t="n">
         <v>229.8299377004603</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K25" t="n">
-        <v>7.54</v>
+        <v>3.69</v>
       </c>
       <c r="L25" t="n">
         <v>4.3</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>19.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43483</v>
+        <v>43486</v>
       </c>
       <c r="H26" t="n">
-        <v>221.35</v>
+        <v>217.2</v>
       </c>
       <c r="I26" t="n">
         <v>218.5153973241119</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.39</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>13.28</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.55</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43521</v>
+        <v>43522</v>
       </c>
       <c r="H27" t="n">
-        <v>214.2</v>
+        <v>220.15</v>
       </c>
       <c r="I27" t="n">
         <v>217.1084925062966</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n">
-        <v>1.38</v>
+        <v>-1.36</v>
       </c>
       <c r="L27" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.44</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.63</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H28" t="n">
-        <v>236.9</v>
+        <v>227.7</v>
       </c>
       <c r="I28" t="n">
         <v>228.6919246370982</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K28" t="n">
-        <v>7.61</v>
+        <v>3.43</v>
       </c>
       <c r="L28" t="n">
         <v>4.38</v>
@@ -2037,7 +2372,7 @@
         <v>0.84</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="O28" t="n">
         <v>2.78</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.84</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H29" t="n">
-        <v>215.85</v>
+        <v>221.8</v>
       </c>
       <c r="I29" t="n">
         <v>220.0564177706644</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K29" t="n">
-        <v>5.2</v>
+        <v>2.59</v>
       </c>
       <c r="L29" t="n">
         <v>4.02</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>14.38</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H30" t="n">
-        <v>211.4</v>
+        <v>198.35</v>
       </c>
       <c r="I30" t="n">
         <v>202.1574479266667</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.69</v>
+        <v>-10.57</v>
       </c>
       <c r="L30" t="n">
-        <v>8.880000000000001</v>
+        <v>12.15</v>
       </c>
       <c r="M30" t="n">
-        <v>0.79</v>
+        <v>5.61</v>
       </c>
       <c r="N30" t="n">
         <v>8.56</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>17.19</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H31" t="n">
-        <v>201.85</v>
+        <v>222.45</v>
       </c>
       <c r="I31" t="n">
         <v>207.9219102302925</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.76</v>
+        <v>-12.15</v>
       </c>
       <c r="L31" t="n">
-        <v>10.71</v>
+        <v>14.24</v>
       </c>
       <c r="M31" t="n">
         <v>4.19</v>
       </c>
       <c r="N31" t="n">
-        <v>6.6</v>
+        <v>10.21</v>
       </c>
       <c r="O31" t="n">
         <v>-6.17</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>16.07</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H32" t="n">
-        <v>203.65</v>
+        <v>201.15</v>
       </c>
       <c r="I32" t="n">
         <v>201.7336204967915</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.449999999999999</v>
+        <v>-9.58</v>
       </c>
       <c r="L32" t="n">
-        <v>11.17</v>
+        <v>11.53</v>
       </c>
       <c r="M32" t="n">
         <v>1.3</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.79</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43818</v>
+        <v>43819</v>
       </c>
       <c r="H33" t="n">
-        <v>220.6</v>
+        <v>230.35</v>
       </c>
       <c r="I33" t="n">
         <v>226.7870321855474</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.67</v>
+        <v>-14.52</v>
       </c>
       <c r="L33" t="n">
         <v>15.24</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>11.16</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43847</v>
+        <v>43850</v>
       </c>
       <c r="H34" t="n">
-        <v>211.95</v>
+        <v>209.15</v>
       </c>
       <c r="I34" t="n">
         <v>210.7905732430254</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.99</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>8.619999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M34" t="n">
         <v>2.17</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>12.28</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43865</v>
+        <v>43866</v>
       </c>
       <c r="H35" t="n">
-        <v>204.5</v>
+        <v>220.8</v>
       </c>
       <c r="I35" t="n">
         <v>216.0327791372135</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>2.22</v>
+        <v>-5.57</v>
       </c>
       <c r="L35" t="n">
-        <v>4.45</v>
+        <v>6.22</v>
       </c>
       <c r="M35" t="n">
         <v>6.81</v>
       </c>
       <c r="N35" t="n">
-        <v>6.23</v>
+        <v>7.97</v>
       </c>
       <c r="O35" t="n">
         <v>-1.32</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>17.38</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43893</v>
+        <v>43894</v>
       </c>
       <c r="H36" t="n">
-        <v>244.95</v>
+        <v>227.1</v>
       </c>
       <c r="I36" t="n">
         <v>231.4762656713306</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>10.94</v>
+        <v>2.85</v>
       </c>
       <c r="L36" t="n">
         <v>6.88</v>
@@ -2493,7 +2924,7 @@
         <v>3.41</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>7.29</v>
       </c>
       <c r="O36" t="n">
         <v>7.97</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>21.14</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H37" t="n">
-        <v>132.75</v>
+        <v>156.3</v>
       </c>
       <c r="I37" t="n">
         <v>153.8814258576464</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K37" t="n">
-        <v>41.55</v>
+        <v>31.18</v>
       </c>
       <c r="L37" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>5.52</v>
+        <v>6.44</v>
       </c>
       <c r="N37" t="n">
-        <v>16.93</v>
+        <v>17.74</v>
       </c>
       <c r="O37" t="n">
         <v>-7.29</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>40.93</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H38" t="n">
-        <v>132.55</v>
+        <v>127.75</v>
       </c>
       <c r="I38" t="n">
         <v>132.47506169545</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K38" t="n">
-        <v>-15.2</v>
+        <v>-18.27</v>
       </c>
       <c r="L38" t="n">
         <v>34.2</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>16.09</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H39" t="n">
-        <v>133.2</v>
+        <v>140</v>
       </c>
       <c r="I39" t="n">
         <v>134.5996591424495</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.27</v>
+        <v>-9.59</v>
       </c>
       <c r="L39" t="n">
-        <v>6.93</v>
+        <v>10.18</v>
       </c>
       <c r="M39" t="n">
         <v>1.48</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>15.53</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44186</v>
+        <v>44187</v>
       </c>
       <c r="H40" t="n">
-        <v>193.35</v>
+        <v>187.6</v>
       </c>
       <c r="I40" t="n">
         <v>190.8565844297321</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K40" t="n">
-        <v>38.11</v>
+        <v>34</v>
       </c>
       <c r="L40" t="n">
         <v>6.25</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>16.33</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44200</v>
+        <v>44201</v>
       </c>
       <c r="H41" t="n">
-        <v>215.35</v>
+        <v>222.85</v>
       </c>
       <c r="I41" t="n">
         <v>218.2095444600875</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-14.79</v>
+        <v>-18.79</v>
       </c>
       <c r="L41" t="n">
-        <v>15.99</v>
+        <v>19.35</v>
       </c>
       <c r="M41" t="n">
         <v>1.3</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>13.29</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H42" t="n">
-        <v>230.2</v>
+        <v>222.2</v>
       </c>
       <c r="I42" t="n">
         <v>225.9589062370641</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>3.3</v>
+        <v>-0.29</v>
       </c>
       <c r="L42" t="n">
         <v>4.98</v>
       </c>
       <c r="M42" t="n">
-        <v>1.77</v>
+        <v>4.08</v>
       </c>
       <c r="N42" t="n">
         <v>4.62</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>19.49</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H43" t="n">
-        <v>258.25</v>
+        <v>266.4</v>
       </c>
       <c r="I43" t="n">
         <v>265.4962354902398</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>-16.22</v>
+        <v>-19.89</v>
       </c>
       <c r="L43" t="n">
-        <v>18.72</v>
+        <v>21.04</v>
       </c>
       <c r="M43" t="n">
         <v>7.02</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>20.28</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44260</v>
+        <v>44263</v>
       </c>
       <c r="H44" t="n">
-        <v>257.85</v>
+        <v>253.15</v>
       </c>
       <c r="I44" t="n">
         <v>253.3781135021105</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.21</v>
+        <v>-4.97</v>
       </c>
       <c r="L44" t="n">
-        <v>4.94</v>
+        <v>5.78</v>
       </c>
       <c r="M44" t="n">
         <v>2.26</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>17.48</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44286</v>
+        <v>44287</v>
       </c>
       <c r="H45" t="n">
-        <v>284.45</v>
+        <v>294.55</v>
       </c>
       <c r="I45" t="n">
         <v>292.8603156459797</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K45" t="n">
-        <v>-12.36</v>
+        <v>-16.35</v>
       </c>
       <c r="L45" t="n">
-        <v>16.26</v>
+        <v>16.85</v>
       </c>
       <c r="M45" t="n">
         <v>1.94</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>12.97</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H46" t="n">
-        <v>293.9</v>
+        <v>260.2</v>
       </c>
       <c r="I46" t="n">
         <v>262.9473113812428</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.22</v>
+        <v>-11.66</v>
       </c>
       <c r="L46" t="n">
-        <v>5.58</v>
+        <v>12.21</v>
       </c>
       <c r="M46" t="n">
-        <v>0.53</v>
+        <v>4.05</v>
       </c>
       <c r="N46" t="n">
-        <v>3.56</v>
+        <v>11.47</v>
       </c>
       <c r="O46" t="n">
         <v>3.55</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>20.06</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44351</v>
+        <v>44354</v>
       </c>
       <c r="H47" t="n">
-        <v>284.65</v>
+        <v>297.5</v>
       </c>
       <c r="I47" t="n">
         <v>297.1068193068987</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K47" t="n">
-        <v>-9.4</v>
+        <v>-14.34</v>
       </c>
       <c r="L47" t="n">
         <v>16.41</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.22</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44410</v>
+        <v>44411</v>
       </c>
       <c r="H48" t="n">
-        <v>275.15</v>
+        <v>267.65</v>
       </c>
       <c r="I48" t="n">
         <v>270.0041524506096</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.51</v>
+        <v>-10.03</v>
       </c>
       <c r="L48" t="n">
         <v>10.87</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.6</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H49" t="n">
-        <v>270.55</v>
+        <v>273.35</v>
       </c>
       <c r="I49" t="n">
         <v>273.3341113607333</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.08</v>
+        <v>-2.13</v>
       </c>
       <c r="L49" t="n">
         <v>3.75</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.82</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H50" t="n">
-        <v>314.2</v>
+        <v>289.35</v>
       </c>
       <c r="I50" t="n">
         <v>291.2153521398109</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K50" t="n">
-        <v>14.94</v>
+        <v>5.85</v>
       </c>
       <c r="L50" t="n">
         <v>6.84</v>
       </c>
       <c r="M50" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="N50" t="n">
-        <v>3.53</v>
+        <v>7.91</v>
       </c>
       <c r="O50" t="n">
         <v>1.03</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>16.72</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44658</v>
+        <v>44659</v>
       </c>
       <c r="H51" t="n">
-        <v>234.8</v>
+        <v>241.45</v>
       </c>
       <c r="I51" t="n">
         <v>239.6357335953219</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K51" t="n">
-        <v>18.85</v>
+        <v>16.55</v>
       </c>
       <c r="L51" t="n">
         <v>7.62</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.24</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44672</v>
+        <v>44673</v>
       </c>
       <c r="H52" t="n">
-        <v>230.15</v>
+        <v>221.6</v>
       </c>
       <c r="I52" t="n">
         <v>222.0222907412721</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.68</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L52" t="n">
         <v>9.550000000000001</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.94</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44680</v>
+        <v>44683</v>
       </c>
       <c r="H53" t="n">
-        <v>240.4</v>
+        <v>246.05</v>
       </c>
       <c r="I53" t="n">
         <v>243.5231363977958</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.48</v>
+        <v>-11.03</v>
       </c>
       <c r="L53" t="n">
         <v>11.82</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>13.24</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44692</v>
+        <v>44693</v>
       </c>
       <c r="H54" t="n">
-        <v>224</v>
+        <v>212.95</v>
       </c>
       <c r="I54" t="n">
         <v>213.4640134384656</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.960000000000001</v>
+        <v>-13.45</v>
       </c>
       <c r="L54" t="n">
-        <v>10.81</v>
+        <v>14.9</v>
       </c>
       <c r="M54" t="n">
         <v>2.45</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>17.5</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="H55" t="n">
-        <v>239.55</v>
+        <v>249.05</v>
       </c>
       <c r="I55" t="n">
         <v>244.748680029052</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.49</v>
+        <v>-16.95</v>
       </c>
       <c r="L55" t="n">
-        <v>14.32</v>
+        <v>17.94</v>
       </c>
       <c r="M55" t="n">
         <v>1.72</v>
       </c>
       <c r="N55" t="n">
-        <v>3.72</v>
+        <v>3.97</v>
       </c>
       <c r="O55" t="n">
         <v>-4.93</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>11.54</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44790</v>
+        <v>44791</v>
       </c>
       <c r="H56" t="n">
-        <v>271.1</v>
+        <v>269.7</v>
       </c>
       <c r="I56" t="n">
         <v>270.8484839452319</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K56" t="n">
-        <v>8.85</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L56" t="n">
         <v>3.39</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.77</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44883</v>
+        <v>44886</v>
       </c>
       <c r="H57" t="n">
-        <v>250.25</v>
+        <v>260.05</v>
       </c>
       <c r="I57" t="n">
         <v>259.3411603243502</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K57" t="n">
-        <v>7.21</v>
+        <v>3.58</v>
       </c>
       <c r="L57" t="n">
         <v>3.19</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.8</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H58" t="n">
-        <v>256.9</v>
+        <v>253.05</v>
       </c>
       <c r="I58" t="n">
         <v>253.2924511884213</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.21</v>
+        <v>-2.69</v>
       </c>
       <c r="L58" t="n">
         <v>4.4</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.19</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H59" t="n">
-        <v>257.8</v>
+        <v>260.75</v>
       </c>
       <c r="I59" t="n">
         <v>258.375773607713</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.88</v>
+        <v>-3.04</v>
       </c>
       <c r="L59" t="n">
         <v>8.039999999999999</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.4</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45048</v>
+        <v>45049</v>
       </c>
       <c r="H60" t="n">
-        <v>265.05</v>
+        <v>263.8</v>
       </c>
       <c r="I60" t="n">
         <v>264.3307958481726</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K60" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="L60" t="n">
         <v>2.05</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45086</v>
+        <v>45089</v>
       </c>
       <c r="H61" t="n">
-        <v>283.45</v>
+        <v>290.45</v>
       </c>
       <c r="I61" t="n">
         <v>284.3782174581468</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.45</v>
+        <v>-10.1</v>
       </c>
       <c r="L61" t="n">
-        <v>9.859999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="M61" t="n">
         <v>0.95</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H62" t="n">
-        <v>376</v>
+        <v>363.25</v>
       </c>
       <c r="I62" t="n">
         <v>364.0241862779679</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K62" t="n">
-        <v>29.45</v>
+        <v>25.06</v>
       </c>
       <c r="L62" t="n">
         <v>4.29</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.27</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="H63" t="n">
-        <v>380.45</v>
+        <v>390.95</v>
       </c>
       <c r="I63" t="n">
         <v>387.5824612846138</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.74</v>
+        <v>-7.63</v>
       </c>
       <c r="L63" t="n">
         <v>11.75</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>10.5</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H64" t="n">
-        <v>458.3</v>
+        <v>453.35</v>
       </c>
       <c r="I64" t="n">
         <v>454.955205174135</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K64" t="n">
-        <v>17.23</v>
+        <v>15.96</v>
       </c>
       <c r="L64" t="n">
         <v>2.66</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>11.34</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H65" t="n">
-        <v>493.2</v>
+        <v>511.3</v>
       </c>
       <c r="I65" t="n">
         <v>504.7658175355958</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.789999999999999</v>
+        <v>-12.78</v>
       </c>
       <c r="L65" t="n">
-        <v>9.02</v>
+        <v>13.23</v>
       </c>
       <c r="M65" t="n">
         <v>1.58</v>
       </c>
       <c r="N65" t="n">
-        <v>3.05</v>
+        <v>3.67</v>
       </c>
       <c r="O65" t="n">
         <v>-1.08</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.52</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H66" t="n">
-        <v>489.6</v>
+        <v>472.2</v>
       </c>
       <c r="I66" t="n">
         <v>472.4792080872487</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.24</v>
+        <v>-7.65</v>
       </c>
       <c r="L66" t="n">
         <v>9.06</v>
@@ -4203,7 +4994,7 @@
         <v>0.92</v>
       </c>
       <c r="N66" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="O66" t="n">
         <v>3.67</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>13.88</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H67" t="n">
-        <v>506.6</v>
+        <v>513.4</v>
       </c>
       <c r="I67" t="n">
         <v>508.1538499028192</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K67" t="n">
-        <v>-7.29</v>
+        <v>-8.73</v>
       </c>
       <c r="L67" t="n">
-        <v>8.109999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="M67" t="n">
         <v>4.08</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.74</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H68" t="n">
-        <v>544.85</v>
+        <v>535.8</v>
       </c>
       <c r="I68" t="n">
         <v>543.5863299049814</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K68" t="n">
-        <v>6.13</v>
+        <v>4.36</v>
       </c>
       <c r="L68" t="n">
         <v>1.42</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>10.24</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45504</v>
+        <v>45505</v>
       </c>
       <c r="H69" t="n">
-        <v>586.4</v>
+        <v>597.85</v>
       </c>
       <c r="I69" t="n">
         <v>590.6924333368044</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.44</v>
+        <v>-11.58</v>
       </c>
       <c r="L69" t="n">
         <v>13.62</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.74</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H70" t="n">
-        <v>681.9</v>
+        <v>667.25</v>
       </c>
       <c r="I70" t="n">
         <v>673.204056440815</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K70" t="n">
-        <v>14.06</v>
+        <v>11.61</v>
       </c>
       <c r="L70" t="n">
         <v>6.06</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>9.26</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H71" t="n">
-        <v>603.95</v>
+        <v>618.85</v>
       </c>
       <c r="I71" t="n">
         <v>616.0889526071309</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K71" t="n">
-        <v>9.49</v>
+        <v>7.25</v>
       </c>
       <c r="L71" t="n">
         <v>4.31</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>10.45</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="H72" t="n">
-        <v>627.5</v>
+        <v>595.4</v>
       </c>
       <c r="I72" t="n">
         <v>598.5908310719217</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K72" t="n">
-        <v>1.4</v>
+        <v>-3.79</v>
       </c>
       <c r="L72" t="n">
-        <v>2.7</v>
+        <v>4.17</v>
       </c>
       <c r="M72" t="n">
         <v>0.82</v>
       </c>
       <c r="N72" t="n">
-        <v>2.63</v>
+        <v>5.12</v>
       </c>
       <c r="O72" t="n">
         <v>2.47</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>12.08</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="H73" t="n">
-        <v>546.15</v>
+        <v>576.75</v>
       </c>
       <c r="I73" t="n">
         <v>574.5956449005016</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K73" t="n">
-        <v>8.27</v>
+        <v>3.13</v>
       </c>
       <c r="L73" t="n">
         <v>5.31</v>
       </c>
       <c r="M73" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="N73" t="n">
-        <v>4.84</v>
+        <v>5.6</v>
       </c>
       <c r="O73" t="n">
         <v>-5.12</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>16.17</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H74" t="n">
-        <v>653.6</v>
+        <v>614</v>
       </c>
       <c r="I74" t="n">
         <v>617.8160255481243</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K74" t="n">
-        <v>13.32</v>
+        <v>6.46</v>
       </c>
       <c r="L74" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="M74" t="n">
-        <v>1.56</v>
+        <v>8.81</v>
       </c>
       <c r="N74" t="n">
-        <v>3.97</v>
+        <v>6.06</v>
       </c>
       <c r="O74" t="n">
         <v>5.6</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>11.81</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H75" t="n">
-        <v>676.05</v>
+        <v>691.75</v>
       </c>
       <c r="I75" t="n">
         <v>686.5138437505592</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K75" t="n">
-        <v>-10.11</v>
+        <v>-12.66</v>
       </c>
       <c r="L75" t="n">
-        <v>10.42</v>
+        <v>13.3</v>
       </c>
       <c r="M75" t="n">
         <v>2.06</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>12.81</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45772</v>
+        <v>45775</v>
       </c>
       <c r="H76" t="n">
-        <v>655.2</v>
+        <v>622</v>
       </c>
       <c r="I76" t="n">
         <v>630.7618718843208</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K76" t="n">
-        <v>-5.28</v>
+        <v>-10.08</v>
       </c>
       <c r="L76" t="n">
-        <v>8.199999999999999</v>
+        <v>13.82</v>
       </c>
       <c r="M76" t="n">
-        <v>-0</v>
+        <v>4.96</v>
       </c>
       <c r="N76" t="n">
         <v>5.95</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>13.75</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="H77" t="n">
-        <v>651.45</v>
+        <v>688.25</v>
       </c>
       <c r="I77" t="n">
         <v>681.8451351302896</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.73</v>
+        <v>-10.65</v>
       </c>
       <c r="L77" t="n">
-        <v>9.949999999999999</v>
+        <v>11.08</v>
       </c>
       <c r="M77" t="n">
         <v>1.6</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>12.67</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="H78" t="n">
-        <v>665.45</v>
+        <v>645.5</v>
       </c>
       <c r="I78" t="n">
         <v>650.5064668536174</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K78" t="n">
-        <v>-3.31</v>
+        <v>-6.21</v>
       </c>
       <c r="L78" t="n">
         <v>6.5</v>
@@ -4887,7 +5822,7 @@
         <v>2.42</v>
       </c>
       <c r="N78" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
         <v>5.65</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>9.85</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H79" t="n">
-        <v>620.05</v>
+        <v>632.85</v>
       </c>
       <c r="I79" t="n">
         <v>626.7361005603848</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K79" t="n">
-        <v>3.94</v>
+        <v>1.96</v>
       </c>
       <c r="L79" t="n">
         <v>3.87</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>7.67</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H80" t="n">
-        <v>1052.5</v>
+        <v>1010</v>
       </c>
       <c r="I80" t="n">
         <v>1011.333633259379</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K80" t="n">
-        <v>66.31</v>
+        <v>59.6</v>
       </c>
       <c r="L80" t="n">
         <v>4.69</v>
@@ -5001,7 +5960,7 @@
         <v>3.28</v>
       </c>
       <c r="N80" t="n">
-        <v>3.56</v>
+        <v>4.04</v>
       </c>
       <c r="O80" t="n">
         <v>2.06</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>7</v>
+      </c>
+      <c r="U80" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>10.43</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H81" t="n">
-        <v>930.65</v>
+        <v>1023.2</v>
       </c>
       <c r="I81" t="n">
         <v>1020.460224637048</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K81" t="n">
-        <v>7.86</v>
+        <v>-1.31</v>
       </c>
       <c r="L81" t="n">
         <v>6.72</v>
@@ -5058,7 +6029,7 @@
         <v>4.99</v>
       </c>
       <c r="N81" t="n">
-        <v>7.67</v>
+        <v>9.94</v>
       </c>
       <c r="O81" t="n">
         <v>-4.04</v>
@@ -5067,7 +6038,19 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>16.56</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H82" t="n">
-        <v>975.95</v>
+        <v>930.45</v>
       </c>
       <c r="I82" t="n">
         <v>936.8676102265374</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K82" t="n">
-        <v>-4.62</v>
+        <v>-9.06</v>
       </c>
       <c r="L82" t="n">
         <v>9.99</v>
@@ -5115,7 +6098,7 @@
         <v>2.67</v>
       </c>
       <c r="N82" t="n">
-        <v>3.62</v>
+        <v>4.66</v>
       </c>
       <c r="O82" t="n">
         <v>9.94</v>
@@ -5124,7 +6107,19 @@
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,25 +6146,25 @@
         <v>13.76</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H83" t="n">
-        <v>954.95</v>
+        <v>1000.65</v>
       </c>
       <c r="I83" t="n">
         <v>963.6071603593721</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K83" t="n">
-        <v>-2.63</v>
+        <v>-7.54</v>
       </c>
       <c r="L83" t="n">
-        <v>5.32</v>
+        <v>8.5</v>
       </c>
       <c r="M83" t="n">
-        <v>2.45</v>
+        <v>5.24</v>
       </c>
       <c r="N83" t="n">
         <v>7.75</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>9.94</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H84" t="n">
-        <v>1109.9</v>
+        <v>1059.1</v>
       </c>
       <c r="I84" t="n">
         <v>1059.728953140134</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K84" t="n">
-        <v>10.92</v>
+        <v>5.84</v>
       </c>
       <c r="L84" t="n">
         <v>2.01</v>
@@ -5238,7 +6245,19 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,14 @@
       <c r="Q85" t="n">
         <v>39</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10247,7 +11274,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.6</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="6">
@@ -10257,7 +11284,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -10267,7 +11294,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8">
@@ -10277,7 +11304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10287,7 +11314,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -10297,7 +11324,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104.4</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -10307,7 +11334,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -10317,7 +11344,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -10327,7 +11354,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="14">
@@ -10337,7 +11364,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.83</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="15">
@@ -10347,7 +11374,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.35</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="16">
@@ -10357,7 +11384,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="17">
@@ -10367,7 +11394,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.31</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="18">
@@ -10377,7 +11404,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="19">
@@ -10387,7 +11414,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.82</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="20">
@@ -10397,7 +11424,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.88</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -10417,7 +11444,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
@@ -10427,7 +11454,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -10437,7 +11464,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="25">
@@ -10447,7 +11474,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.02</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="26">
@@ -10457,7 +11484,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.22</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="27">
@@ -10467,7 +11494,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.93</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="28">
@@ -10477,7 +11504,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
